--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A192C7-FF38-42CB-BEE1-07EBF3F566CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84344E91-C448-4E10-9095-B4B37A19B194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
   <si>
     <t>Date</t>
   </si>
@@ -298,6 +298,12 @@
   </si>
   <si>
     <t>Values with Equal Array Remainders</t>
+  </si>
+  <si>
+    <t>leet POTD</t>
+  </si>
+  <si>
+    <t>Matrix overlapping</t>
   </si>
 </sst>
 </file>
@@ -1139,8 +1145,21 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="2"/>
-      <c r="D29" s="3"/>
+      <c r="A29" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84344E91-C448-4E10-9095-B4B37A19B194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED4C626-E2E1-4BC5-99CB-3050AF6C2CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
@@ -304,6 +304,15 @@
   </si>
   <si>
     <t>Matrix overlapping</t>
+  </si>
+  <si>
+    <t>Strivers</t>
+  </si>
+  <si>
+    <t>Linked List</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searching </t>
   </si>
 </sst>
 </file>
@@ -1162,8 +1171,21 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="2"/>
-      <c r="D30" s="3"/>
+      <c r="A30" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED4C626-E2E1-4BC5-99CB-3050AF6C2CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8259C5F2-F431-4D9E-A62B-D58F86677C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t xml:space="preserve">Searching </t>
+  </si>
+  <si>
+    <t>Dominant pair</t>
   </si>
 </sst>
 </file>
@@ -1188,8 +1191,21 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="2"/>
-      <c r="D31" s="3"/>
+      <c r="A31" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8259C5F2-F431-4D9E-A62B-D58F86677C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9385FE-C9E6-4975-B400-50D5E7F0470C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -316,6 +316,12 @@
   </si>
   <si>
     <t>Dominant pair</t>
+  </si>
+  <si>
+    <t>Double linked List</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Intro</t>
   </si>
 </sst>
 </file>
@@ -1208,8 +1214,21 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="2"/>
-      <c r="D32" s="3"/>
+      <c r="A32" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9385FE-C9E6-4975-B400-50D5E7F0470C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F777B646-FB88-47EF-A8FF-F6C8604C229A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
   <si>
     <t>Date</t>
   </si>
@@ -322,6 +322,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Intro</t>
+  </si>
+  <si>
+    <t>Binary Tree</t>
+  </si>
+  <si>
+    <t>Min Abs Diff</t>
   </si>
 </sst>
 </file>
@@ -1230,67 +1236,80 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4">
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="2"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:5">
       <c r="A35" s="2"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" s="2"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="2"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:5">
       <c r="A38" s="2"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="2"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:5">
       <c r="A40" s="2"/>
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" s="2"/>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:5">
       <c r="A42" s="2"/>
       <c r="D42" s="3"/>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:5">
       <c r="A43" s="2"/>
       <c r="D43" s="3"/>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:5">
       <c r="A44" s="2"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:5">
       <c r="A45" s="2"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:5">
       <c r="A46" s="2"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:5">
       <c r="A47" s="2"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:5">
       <c r="A48" s="2"/>
       <c r="D48" s="3"/>
     </row>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F777B646-FB88-47EF-A8FF-F6C8604C229A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A520D2B1-F600-4C1B-93F3-27C634A1D895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -328,6 +328,12 @@
   </si>
   <si>
     <t>Min Abs Diff</t>
+  </si>
+  <si>
+    <t>Reverse Degree String</t>
+  </si>
+  <si>
+    <t>Reverse degree for all the char in strings</t>
   </si>
 </sst>
 </file>
@@ -1254,8 +1260,21 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="2"/>
-      <c r="D34" s="3"/>
+      <c r="A34" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A520D2B1-F600-4C1B-93F3-27C634A1D895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3907A603-50AA-433A-9C27-4D6F5BDB2931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -334,6 +334,12 @@
   </si>
   <si>
     <t>Reverse degree for all the char in strings</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>Exam for intership</t>
   </si>
 </sst>
 </file>
@@ -1277,8 +1283,23 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="2"/>
-      <c r="D35" s="3"/>
+      <c r="A35" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="3">
+        <f>--E35</f>
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <f>--E36</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3907A603-50AA-433A-9C27-4D6F5BDB2931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDF447E-BCB7-4180-BD09-43B1421EE303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1308" yWindow="3792" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="91">
   <si>
     <t>Date</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>Exam for intership</t>
+  </si>
+  <si>
+    <t>Sliding window</t>
+  </si>
+  <si>
+    <t>Min opera to reduce x</t>
   </si>
 </sst>
 </file>
@@ -1292,18 +1298,31 @@
       <c r="C35" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="e">
         <f>--E35</f>
-        <v>0</v>
-      </c>
-      <c r="E35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E35" t="e">
         <f>--E36</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="2"/>
-      <c r="D36" s="3"/>
+      <c r="A36" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDF447E-BCB7-4180-BD09-43B1421EE303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385362C0-7F94-49F0-AA02-17ADBAAB4DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1308" yWindow="3792" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1308" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
   <si>
     <t>Date</t>
   </si>
@@ -346,6 +346,15 @@
   </si>
   <si>
     <t>Min opera to reduce x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Striver POTD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix </t>
+  </si>
+  <si>
+    <t>peak element value in matrix</t>
   </si>
 </sst>
 </file>
@@ -1325,8 +1334,21 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="2"/>
-      <c r="D37" s="3"/>
+      <c r="A37" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385362C0-7F94-49F0-AA02-17ADBAAB4DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2E39D2-5BE3-41B4-9140-6490E193880E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1308" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -355,6 +355,15 @@
   </si>
   <si>
     <t>peak element value in matrix</t>
+  </si>
+  <si>
+    <t>Potd GFG &amp; Striver</t>
+  </si>
+  <si>
+    <t>Maths &amp; String</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first and last as uppercase &amp; max cost pizza </t>
   </si>
 </sst>
 </file>
@@ -1351,8 +1360,21 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="2"/>
-      <c r="D38" s="3"/>
+      <c r="A38" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2E39D2-5BE3-41B4-9140-6490E193880E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65801738-5481-4FE7-BD0E-70C8235CBFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1308" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -364,6 +364,21 @@
   </si>
   <si>
     <t xml:space="preserve">first and last as uppercase &amp; max cost pizza </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 to 5th Oct </t>
+  </si>
+  <si>
+    <t>Exams</t>
+  </si>
+  <si>
+    <t>Min to add to make valid</t>
+  </si>
+  <si>
+    <t>Min numbers of parenthesis to make a string valid</t>
+  </si>
+  <si>
+    <t>Complete</t>
   </si>
 </sst>
 </file>
@@ -1377,12 +1392,34 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="2">
+        <f>-D39-E39-A40</f>
+        <v>-46301</v>
+      </c>
       <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="2"/>
-      <c r="D40" s="3"/>
+      <c r="A40" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65801738-5481-4FE7-BD0E-70C8235CBFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5736834C-7873-4639-96C8-2E1434992A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1308" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -379,6 +379,12 @@
   </si>
   <si>
     <t>Complete</t>
+  </si>
+  <si>
+    <t>Remove outmost parenthesis</t>
+  </si>
+  <si>
+    <t>Use string Builder to make new string</t>
   </si>
 </sst>
 </file>
@@ -1422,8 +1428,21 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="2"/>
-      <c r="D41" s="3"/>
+      <c r="A41" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5736834C-7873-4639-96C8-2E1434992A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDD7D54-EA6C-474E-9839-E542984172D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1308" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10968" yWindow="3684" windowWidth="10884" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="106">
   <si>
     <t>Date</t>
   </si>
@@ -385,6 +385,12 @@
   </si>
   <si>
     <t>Use string Builder to make new string</t>
+  </si>
+  <si>
+    <t>Min steps to reach n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiply if even else odd </t>
   </si>
 </sst>
 </file>
@@ -1445,8 +1451,21 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="2"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E42" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2"/>
